--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>21/09 15:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>250</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>21/09 15:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>21/09 12:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>140</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>23/09 15:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>21/09 12:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>150</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>140</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>21/09 12:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>150</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>150</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>23/09 16:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>140</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>140</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>125</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>21/09 17:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>125</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>140</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>23/09 15:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>23/09 16:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>125</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>125</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>23/09 15:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>125</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>125</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>125</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45921.07354980466</v>
+        <v>45921.07354980324</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Pioneers VorarlbergAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+109%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45921.13175993031</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>140</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,142 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45921.13175993031</v>
+        <v>45921.13175993055</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EC Villach</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EC Villacher SV – Pustertal WolfeICE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>21/09 15:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+207%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45921.18365899439</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Bili Tygri</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bili Tygri Liberec – HC Rytiri KladnoExtraliga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>21/09 15:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+88,1%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45921.18365899439</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Vaasan Spo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Vaasan Sport – Jukurit MikkeliLiiga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>23/09 15:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+69,9%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45921.18365899439</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -1623,10 +1623,8 @@
           <t>21/09 15:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>200</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45921.18365899439</v>
+        <v>45921.18365899305</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>125</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45921.18365899439</v>
+        <v>45921.18365899305</v>
       </c>
     </row>
     <row r="30">
@@ -1713,10 +1709,8 @@
           <t>23/09 15:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>110</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1729,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45921.18365899439</v>
+        <v>45921.18365899305</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,51 @@
         <v>45921.18365899305</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Mich</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Dukla Michalovce – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+123%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45921.27112770905</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>150</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,52 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45921.27112770905</v>
+        <v>45921.27112770834</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Kometa </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HC Kometa Brno – HC PlzenExtraliga (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>23/09 16:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+67,5%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45921.30375622506</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>23/09 16:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>110</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,187 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45921.30375622506</v>
+        <v>45921.30375622685</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | FTC-Teleko</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FTC-Telekom – Innsbruck Die HaieAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21/09 13:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+218%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45921.34972262354</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Vitkovice </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Vitkovice – LiberecRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>23/09 15:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+122%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45921.34972262354</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Augsbourg </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Augsbourg – IserlohnDEL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>21/09 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45921.34972262354</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – ERC IngolstadtDEL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+83,5%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45921.34972262354</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>21/09 13:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>225</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45921.34972262354</v>
+        <v>45921.34972262732</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>23/09 15:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>150</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45921.34972262354</v>
+        <v>45921.34972262732</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>21/09 17:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45921.34972262354</v>
+        <v>45921.34972262732</v>
       </c>
     </row>
     <row r="36">
@@ -1973,23 +1967,201 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>125</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+83,5%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45921.34972262732</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Wolfsburg </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wolfsburg Grizzly – DresdnerAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>21/09 14:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45921.38804300482</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | MSHK Zilin</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MSHK Zilina – HK PopradExtraliga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>21/09 15:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+118%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45921.38804300482</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Tappara Ta</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tappara Tampere – TPS TurkuLiiga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>23/09 15:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>+83,5%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>45921.34972262354</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+90,9%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45921.38804300482</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Malmo Redh</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Malmo Redhawks – Brynas IFSHL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+86,2%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45921.38804300482</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>21/09 14:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>200</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45921.38804300482</v>
+        <v>45921.38804300926</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>150</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45921.38804300482</v>
+        <v>45921.38804300926</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>23/09 15:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>125</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45921.38804300482</v>
+        <v>45921.38804300926</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>125</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,97 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45921.38804300482</v>
+        <v>45921.38804300926</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nurnberg I</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nurnberg Ice Tigers – Kölner HaieAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21/09 12:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+128%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45921.43058330187</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kladno – P</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Kladno – PardubiceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23/09 16:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45921.43058330187</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>21/09 12:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>175</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45921.43058330187</v>
+        <v>45921.43058329861</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>23/09 16:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>140</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,52 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45921.43058330187</v>
+        <v>45921.43058329861</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sport Vaas</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sport Vaasa – JukuritFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/09 15:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+81,0%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45921.52708261831</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>23/09 15:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>125</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,142 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45921.52708261831</v>
+        <v>45921.52708261574</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – HC PresovExtraliga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21/09 14:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+188%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45921.5582677132</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mhk 32 Lip</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Mhk 32 Liptovsky Mikulas – HKM AS ZvolenExtraliga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21/09 15:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+160%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45921.5582677132</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Farjestads</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Farjestads BK – Frölunda HCSHL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+74,9%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45921.5582677132</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>21/09 14:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>200</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45921.5582677132</v>
+        <v>45921.55826770834</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>21/09 15:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>175</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45921.5582677132</v>
+        <v>45921.55826770834</v>
       </c>
     </row>
     <row r="46">
@@ -2401,23 +2397,156 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>110</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+74,9%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45921.55826770834</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rapperswil</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Rapperswil Jona Lakers – EHC Biel-BienneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>23/09 17:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+65,9%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45921.59547692979</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Djurgården</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Djurgårdens IF – Frölunda HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>23/09 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>110.00</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>+74,9%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>45921.5582677132</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+64,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45921.59547692979</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lulea HF –</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lulea HF – Djurgaardens IFSHL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+59,9%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45921.59547692979</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>100</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45921.59547692979</v>
+        <v>45921.59547693287</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>23/09 17:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>110</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45921.59547692979</v>
+        <v>45921.59547693287</v>
       </c>
     </row>
     <row r="49">
@@ -2530,23 +2526,381 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+59,9%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45921.59547693287</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Vaxjo Lake</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vaxjo Lakers – Orebro HKSHL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>1,60%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>+59,9%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>45921.59547692979</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+59,1%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45921.63813174004</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Leksands I</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Leksands IF – Skelleftea AIKSHL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+58,1%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45921.63813174004</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lugano – B</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Lugano – BernSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>23/09 17:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>91.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+52,5%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45921.63813174004</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fribourg G</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fribourg Gotteron – ZSC LionsSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>23/09 17:45</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>88.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+50,8%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45921.63813174004</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Trinec – M</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Trinec – Mountfield HKRép.Tchèque - Extraliga</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>23/09 15:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+48,5%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45921.63813174004</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Bolz</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>KAC – BolzanoAutriche - Autriche ICE - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21/09 15:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+47,7%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45921.63813174004</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Red Star K</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Red Star Kunlun – Torpedo Nijni NovgorodRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>22/09 16:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+46,6%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45921.63813174004</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rosario Ce</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Rosario Central – Talleres de CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>21/09 22:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+46,1%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45921.63813174004</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>100</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>100</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>91.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>91</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
       </c>
     </row>
     <row r="53">
@@ -2704,10 +2698,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>88.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>88</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2720,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
       </c>
     </row>
     <row r="54">
@@ -2749,10 +2741,8 @@
           <t>23/09 15:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>100</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2765,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
       </c>
     </row>
     <row r="55">
@@ -2794,10 +2784,8 @@
           <t>21/09 15:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>93</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2810,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
       </c>
     </row>
     <row r="56">
@@ -2839,10 +2827,8 @@
           <t>22/09 16:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>101</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2855,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
       </c>
     </row>
     <row r="57">
@@ -2884,10 +2870,8 @@
           <t>21/09 22:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>60</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2900,7 +2884,232 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45921.63813174004</v>
+        <v>45921.63813173611</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | EHC Kloten</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EHC Kloten – HC AjoieSuisse - NLA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>23/09 17:45</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+87,2%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45921.68285820571</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ocelari Tr</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ocelari Trinec – Mountfield HKExtraliga</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>23/09 15:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+63,0%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45921.68285820571</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Karlovy Va</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Karlovy Vary – Ceske BudejoviceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>23/09 16:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>98.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+47,2%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45921.68285820571</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Dinamo Min</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dinamo Minsk – HC BarysRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>22/09 16:10</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+45,0%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45921.68285820571</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Litvinov –</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Litvinov – Mlada BoleslavRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>23/09 15:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>96.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+45,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45921.68285820571</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>100</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45921.68285820571</v>
+        <v>45921.68285820602</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>23/09 15:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>110</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45921.68285820571</v>
+        <v>45921.68285820602</v>
       </c>
     </row>
     <row r="60">
@@ -3003,10 +2999,8 @@
           <t>23/09 16:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>98.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>98</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3019,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45921.68285820571</v>
+        <v>45921.68285820602</v>
       </c>
     </row>
     <row r="61">
@@ -3048,10 +3042,8 @@
           <t>22/09 16:10</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>101</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3064,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45921.68285820571</v>
+        <v>45921.68285820602</v>
       </c>
     </row>
     <row r="62">
@@ -3093,10 +3085,8 @@
           <t>23/09 15:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>96.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>96</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3109,7 +3099,412 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45921.68285820571</v>
+        <v>45921.68285820602</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Kloten</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EHC Kloten – HC Ajoie PorrentruyNational League A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>23/09 17:45</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – LukkoFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+87,5%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Olomouc – </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Olomouc – Sparta PragueRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>23/09 16:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+77,4%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Växjö Lake</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Växjö Lakers HC – Örebro HKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+70,9%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Leksands I</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Leksands IF – Skellefteå AIKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+68,7%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Luleå HF –</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Luleå HF – Djurgårdens IFSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+67,7%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HIFK – Pel</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HIFK – Pelicans LahtiFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+63,1%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | SKA Saint </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SKA Saint Pétersbourg – HK Avangard OmskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>23/09 16:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+48,6%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45921.7198984747</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rögle BK –</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rögle BK – Linköpings HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+47,4%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45921.7198984747</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>150</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>125</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>23/09 16:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>125</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="66">
@@ -3263,10 +3257,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>110</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3279,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="67">
@@ -3308,10 +3300,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>110</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3324,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="68">
@@ -3353,10 +3343,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>110</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3369,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="69">
@@ -3398,10 +3386,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>110</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3414,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="70">
@@ -3443,10 +3429,8 @@
           <t>23/09 16:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>101</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3459,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
       </c>
     </row>
     <row r="71">
@@ -3488,10 +3472,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>94</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3504,7 +3486,97 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45921.7198984747</v>
+        <v>45921.71989847222</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SC Rappers</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SC Rapperswil-Jona Lakers – EHC BielNational League A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>23/09 17:45</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+61,9%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45921.7690246909</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HV71 – Tim</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HV71 – Timrå IKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+47,3%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45921.7690246909</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>23/09 17:45</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>100</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45921.7690246909</v>
+        <v>45921.7690246875</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>93</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,187 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45921.7690246909</v>
+        <v>45921.7690246875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ilves Tamp</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ilves Tampere – JYP JyväskyläFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+104%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45921.8023978971</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Graz 99ers</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Graz 99ers – Fehervar AV19Autriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>23/09 16:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+101%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45921.8023978971</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | K-Espoo – </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>K-Espoo – SaiPaFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+82,5%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45921.8023978971</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KalPa – As</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>KalPa – Assät PoriFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>98.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+50,3%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45921.8023978971</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3601,10 +3601,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>140</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3617,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45921.8023978971</v>
+        <v>45921.80239789352</v>
       </c>
     </row>
     <row r="75">
@@ -3646,10 +3644,8 @@
           <t>23/09 16:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>140</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3662,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45921.8023978971</v>
+        <v>45921.80239789352</v>
       </c>
     </row>
     <row r="76">
@@ -3691,10 +3687,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>125</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3707,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45921.8023978971</v>
+        <v>45921.80239789352</v>
       </c>
     </row>
     <row r="77">
@@ -3736,10 +3730,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>98.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>98</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3752,7 +3744,142 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45921.8023978971</v>
+        <v>45921.80239789352</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – Lukko RaumaLiiga</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45921.84819544534</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ilves Tamp</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ilves Tampere – JYP JyvaskylaLiiga</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+95,1%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45921.84819544534</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Energie Ka</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Energie Karlovy Vary – Ceske BudejoviceExtraliga</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>23/09 16:00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+54,6%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45921.84819544534</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -3773,10 +3773,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>140</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3789,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45921.84819544534</v>
+        <v>45921.84819543982</v>
       </c>
     </row>
     <row r="79">
@@ -3818,10 +3816,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>125</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3834,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45921.84819544534</v>
+        <v>45921.84819543982</v>
       </c>
     </row>
     <row r="80">
@@ -3863,10 +3859,8 @@
           <t>23/09 16:00</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>100</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3879,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45921.84819544534</v>
+        <v>45921.84819543982</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3876,6 +3876,96 @@
         <v>45921.84819543982</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Färjestad </t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Färjestad BK – Frölunda HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>25/09 17:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+70,2%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45921.92951872585</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | HIFK Hocke</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HIFK Hockey – PelicansFinlande - Liiga</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>24/09 15:30</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+48,0%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45921.92951872585</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-21.xlsx
+++ b/data/valuebets_database_2025-09-21.xlsx
@@ -3902,10 +3902,8 @@
           <t>25/09 17:00</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>110</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3918,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45921.92951872585</v>
+        <v>45921.92951872685</v>
       </c>
     </row>
     <row r="82">
@@ -3947,10 +3945,8 @@
           <t>24/09 15:30</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>94</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3963,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45921.92951872585</v>
+        <v>45921.92951872685</v>
       </c>
     </row>
   </sheetData>
